--- a/src_files/data_files/hydroUpd-v1.xlsx
+++ b/src_files/data_files/hydroUpd-v1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BB\bb-dev\north_european_model\src_files\data_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4288721C-C904-462F-92B8-C6DA952B77CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82C34CFA-97C4-428F-85F9-4A4300EFBEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="747" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,29 +42,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="118">
   <si>
     <t>AT00</t>
   </si>
   <si>
-    <t>PS Closed pump</t>
-  </si>
-  <si>
-    <t>PS Closed turbine</t>
-  </si>
-  <si>
-    <t>PS Open pump</t>
-  </si>
-  <si>
-    <t>PS Open turbine</t>
-  </si>
-  <si>
-    <t>Reservoir</t>
-  </si>
-  <si>
-    <t>Run-of-River</t>
-  </si>
-  <si>
     <t>BE00</t>
   </si>
   <si>
@@ -122,9 +104,6 @@
     <t>Country</t>
   </si>
   <si>
-    <t>Generator_ID</t>
-  </si>
-  <si>
     <t>Scenario</t>
   </si>
   <si>
@@ -384,6 +363,39 @@
   </si>
   <si>
     <t>##</t>
+  </si>
+  <si>
+    <t>unittype</t>
+  </si>
+  <si>
+    <t>rorTurbine</t>
+  </si>
+  <si>
+    <t>reservoirTurbine</t>
+  </si>
+  <si>
+    <t>psopenturbine</t>
+  </si>
+  <si>
+    <t>psopenpump</t>
+  </si>
+  <si>
+    <t>psclosedturbine</t>
+  </si>
+  <si>
+    <t>psclosedpump</t>
+  </si>
+  <si>
+    <t>psOpenTurbine</t>
+  </si>
+  <si>
+    <t>psOpenPump</t>
+  </si>
+  <si>
+    <t>psClosedTurbine</t>
+  </si>
+  <si>
+    <t>psClosedPump</t>
   </si>
 </sst>
 </file>
@@ -1110,37 +1122,46 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="1">
-          <cell r="C1" t="str">
-            <v>Generator_ID</v>
+          <cell r="D1" t="str">
+            <v>unittype</v>
           </cell>
           <cell r="S1" t="str">
             <v>vomCosts</v>
           </cell>
           <cell r="Y1" t="str">
-            <v>disabled-rampUpCost</v>
+            <v>##rampUpCost</v>
           </cell>
           <cell r="Z1" t="str">
-            <v>disabled-rampDownCost</v>
+            <v>##rampDownCost</v>
           </cell>
         </row>
         <row r="3">
-          <cell r="C3" t="str">
-            <v>Onshore Wind</v>
+          <cell r="D3" t="str">
+            <v>windOnshore</v>
+          </cell>
+          <cell r="S3">
+            <v>1.75</v>
           </cell>
         </row>
         <row r="4">
-          <cell r="C4" t="str">
-            <v>Offshore Wind</v>
+          <cell r="D4" t="str">
+            <v>windOffshore</v>
+          </cell>
+          <cell r="S4">
+            <v>2</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="C5" t="str">
-            <v>Solar PV</v>
+          <cell r="D5" t="str">
+            <v>solarPV</v>
+          </cell>
+          <cell r="S5">
+            <v>1.5</v>
           </cell>
         </row>
         <row r="7">
-          <cell r="C7" t="str">
-            <v>Run-of-River</v>
+          <cell r="D7" t="str">
+            <v>rorTurbine</v>
           </cell>
           <cell r="S7">
             <v>2</v>
@@ -1153,8 +1174,8 @@
           </cell>
         </row>
         <row r="8">
-          <cell r="C8" t="str">
-            <v>Reservoir</v>
+          <cell r="D8" t="str">
+            <v>reservoirTurbine</v>
           </cell>
           <cell r="S8">
             <v>1.8</v>
@@ -1167,8 +1188,8 @@
           </cell>
         </row>
         <row r="9">
-          <cell r="C9" t="str">
-            <v>PS Open turbine</v>
+          <cell r="D9" t="str">
+            <v>psOpenTurbine</v>
           </cell>
           <cell r="S9">
             <v>2</v>
@@ -1181,8 +1202,8 @@
           </cell>
         </row>
         <row r="10">
-          <cell r="C10" t="str">
-            <v>PS Open pump</v>
+          <cell r="D10" t="str">
+            <v>psOpenPump</v>
           </cell>
           <cell r="S10">
             <v>1.6</v>
@@ -1195,8 +1216,8 @@
           </cell>
         </row>
         <row r="11">
-          <cell r="C11" t="str">
-            <v>PS Closed turbine</v>
+          <cell r="D11" t="str">
+            <v>psClosedTurbine</v>
           </cell>
           <cell r="S11">
             <v>1.8</v>
@@ -1209,8 +1230,8 @@
           </cell>
         </row>
         <row r="12">
-          <cell r="C12" t="str">
-            <v>PS Closed pump</v>
+          <cell r="D12" t="str">
+            <v>psClosedPump</v>
           </cell>
           <cell r="S12">
             <v>1.4</v>
@@ -1223,8 +1244,8 @@
           </cell>
         </row>
         <row r="14">
-          <cell r="C14" t="str">
-            <v>Oil shale old</v>
+          <cell r="D14" t="str">
+            <v>oilShaleOld</v>
           </cell>
           <cell r="S14">
             <v>3.3</v>
@@ -1237,8 +1258,8 @@
           </cell>
         </row>
         <row r="15">
-          <cell r="C15" t="str">
-            <v>Oil shale new Bio</v>
+          <cell r="D15" t="str">
+            <v>bioOilshaleNew</v>
           </cell>
           <cell r="S15">
             <v>3.3</v>
@@ -1251,8 +1272,8 @@
           </cell>
         </row>
         <row r="16">
-          <cell r="C16" t="str">
-            <v>Oil shale new</v>
+          <cell r="D16" t="str">
+            <v>oilshaleNew</v>
           </cell>
           <cell r="S16">
             <v>3.3</v>
@@ -1265,8 +1286,8 @@
           </cell>
         </row>
         <row r="17">
-          <cell r="C17" t="str">
-            <v>Lignite old 2 Bio</v>
+          <cell r="D17" t="str">
+            <v>bioLigniteOld2</v>
           </cell>
           <cell r="S17">
             <v>3.3</v>
@@ -1279,8 +1300,8 @@
           </cell>
         </row>
         <row r="18">
-          <cell r="C18" t="str">
-            <v>Lignite old 2</v>
+          <cell r="D18" t="str">
+            <v>ligniteOld2</v>
           </cell>
           <cell r="S18">
             <v>3.3</v>
@@ -1293,8 +1314,8 @@
           </cell>
         </row>
         <row r="19">
-          <cell r="C19" t="str">
-            <v>Lignite old 1 Bio</v>
+          <cell r="D19" t="str">
+            <v>bioLigniteOld1</v>
           </cell>
           <cell r="S19">
             <v>3.3</v>
@@ -1307,8 +1328,8 @@
           </cell>
         </row>
         <row r="20">
-          <cell r="C20" t="str">
-            <v>Lignite old 1</v>
+          <cell r="D20" t="str">
+            <v>ligniteOld1</v>
           </cell>
           <cell r="S20">
             <v>3.3</v>
@@ -1321,8 +1342,8 @@
           </cell>
         </row>
         <row r="21">
-          <cell r="C21" t="str">
-            <v>Lignite new</v>
+          <cell r="D21" t="str">
+            <v>ligniteNew</v>
           </cell>
           <cell r="S21">
             <v>3.3</v>
@@ -1335,8 +1356,8 @@
           </cell>
         </row>
         <row r="22">
-          <cell r="C22" t="str">
-            <v>Lignite CCS</v>
+          <cell r="D22" t="str">
+            <v>ligniteCCS</v>
           </cell>
           <cell r="S22">
             <v>6.6</v>
@@ -1349,8 +1370,8 @@
           </cell>
         </row>
         <row r="23">
-          <cell r="C23" t="str">
-            <v>Light oil</v>
+          <cell r="D23" t="str">
+            <v>OilLightOld</v>
           </cell>
           <cell r="S23">
             <v>2.1</v>
@@ -1363,8 +1384,8 @@
           </cell>
         </row>
         <row r="24">
-          <cell r="C24" t="str">
-            <v>Heavy oil old 2</v>
+          <cell r="D24" t="str">
+            <v>oilHeavyOld2</v>
           </cell>
           <cell r="S24">
             <v>3.3</v>
@@ -1377,8 +1398,8 @@
           </cell>
         </row>
         <row r="25">
-          <cell r="C25" t="str">
-            <v>Heavy oil old 1</v>
+          <cell r="D25" t="str">
+            <v>oilHeavyOld1</v>
           </cell>
           <cell r="S25">
             <v>3.3</v>
@@ -1391,8 +1412,8 @@
           </cell>
         </row>
         <row r="26">
-          <cell r="C26" t="str">
-            <v>Heavy oil old 1 Bio</v>
+          <cell r="D26" t="str">
+            <v>bioOilHeavyOld</v>
           </cell>
           <cell r="S26">
             <v>3.3</v>
@@ -1405,8 +1426,8 @@
           </cell>
         </row>
         <row r="27">
-          <cell r="C27" t="str">
-            <v>Hard coal old 1 Bio</v>
+          <cell r="D27" t="str">
+            <v>bioCoalOld</v>
           </cell>
           <cell r="S27">
             <v>3.3</v>
@@ -1419,8 +1440,8 @@
           </cell>
         </row>
         <row r="28">
-          <cell r="C28" t="str">
-            <v>Hard coal old 2 Bio</v>
+          <cell r="D28" t="str">
+            <v>bioCoalOld2</v>
           </cell>
           <cell r="S28">
             <v>3.3</v>
@@ -1433,8 +1454,8 @@
           </cell>
         </row>
         <row r="29">
-          <cell r="C29" t="str">
-            <v>Hard coal old 2</v>
+          <cell r="D29" t="str">
+            <v>coalOld2</v>
           </cell>
           <cell r="S29">
             <v>3.3</v>
@@ -1447,8 +1468,8 @@
           </cell>
         </row>
         <row r="30">
-          <cell r="C30" t="str">
-            <v>Hard coal old 1</v>
+          <cell r="D30" t="str">
+            <v>coalOld1</v>
           </cell>
           <cell r="S30">
             <v>3.3</v>
@@ -1461,8 +1482,8 @@
           </cell>
         </row>
         <row r="31">
-          <cell r="C31" t="str">
-            <v>Hard coal new Bio</v>
+          <cell r="D31" t="str">
+            <v>bioCoalNew</v>
           </cell>
           <cell r="S31">
             <v>3.3</v>
@@ -1475,8 +1496,8 @@
           </cell>
         </row>
         <row r="32">
-          <cell r="C32" t="str">
-            <v>Hard coal new</v>
+          <cell r="D32" t="str">
+            <v>coalNew</v>
           </cell>
           <cell r="S32">
             <v>3.3</v>
@@ -1489,8 +1510,8 @@
           </cell>
         </row>
         <row r="33">
-          <cell r="C33" t="str">
-            <v>Gas conventional old 2 Bio</v>
+          <cell r="D33" t="str">
+            <v>bioGasOld2</v>
           </cell>
           <cell r="S33">
             <v>2.1</v>
@@ -1503,8 +1524,8 @@
           </cell>
         </row>
         <row r="34">
-          <cell r="C34" t="str">
-            <v>Gas conventional old 2</v>
+          <cell r="D34" t="str">
+            <v>gasOld2</v>
           </cell>
           <cell r="S34">
             <v>2.1</v>
@@ -1517,8 +1538,8 @@
           </cell>
         </row>
         <row r="35">
-          <cell r="C35" t="str">
-            <v>Gas conventional old 1</v>
+          <cell r="D35" t="str">
+            <v>gasOld1</v>
           </cell>
           <cell r="S35">
             <v>2.1</v>
@@ -1531,8 +1552,8 @@
           </cell>
         </row>
         <row r="36">
-          <cell r="C36" t="str">
-            <v>Gas OCGT old</v>
+          <cell r="D36" t="str">
+            <v>gasOCGTold</v>
           </cell>
           <cell r="S36">
             <v>2.6</v>
@@ -1545,8 +1566,8 @@
           </cell>
         </row>
         <row r="37">
-          <cell r="C37" t="str">
-            <v>Gas OCGT new</v>
+          <cell r="D37" t="str">
+            <v>gasOCGTnew</v>
           </cell>
           <cell r="S37">
             <v>2.6</v>
@@ -1559,8 +1580,8 @@
           </cell>
         </row>
         <row r="38">
-          <cell r="C38" t="str">
-            <v>Gas CCGT present 2</v>
+          <cell r="D38" t="str">
+            <v>gasCCGTpresent2</v>
           </cell>
           <cell r="S38">
             <v>2.6</v>
@@ -1573,8 +1594,8 @@
           </cell>
         </row>
         <row r="39">
-          <cell r="C39" t="str">
-            <v>Gas CCGT present 1</v>
+          <cell r="D39" t="str">
+            <v>gasCCGTpresent1</v>
           </cell>
           <cell r="S39">
             <v>2.6</v>
@@ -1587,8 +1608,8 @@
           </cell>
         </row>
         <row r="40">
-          <cell r="C40" t="str">
-            <v>Gas CCGT old 2 Bio</v>
+          <cell r="D40" t="str">
+            <v>bioGasCCGTOld2</v>
           </cell>
           <cell r="S40">
             <v>2.6</v>
@@ -1601,8 +1622,8 @@
           </cell>
         </row>
         <row r="41">
-          <cell r="C41" t="str">
-            <v>Gas CCGT old 2</v>
+          <cell r="D41" t="str">
+            <v>gasCCGTOld2</v>
           </cell>
           <cell r="S41">
             <v>2.6</v>
@@ -1615,8 +1636,8 @@
           </cell>
         </row>
         <row r="42">
-          <cell r="C42" t="str">
-            <v>Gas CCGT old 1</v>
+          <cell r="D42" t="str">
+            <v>gasCCGTOld1</v>
           </cell>
           <cell r="S42">
             <v>2.6</v>
@@ -1629,8 +1650,8 @@
           </cell>
         </row>
         <row r="43">
-          <cell r="C43" t="str">
-            <v>Gas CCGT new</v>
+          <cell r="D43" t="str">
+            <v>gasCCGTNew</v>
           </cell>
           <cell r="S43">
             <v>2.6</v>
@@ -1643,8 +1664,8 @@
           </cell>
         </row>
         <row r="45">
-          <cell r="C45" t="str">
-            <v>Hard coal CCS</v>
+          <cell r="D45" t="str">
+            <v>coalCCS</v>
           </cell>
           <cell r="S45">
             <v>6.6</v>
@@ -1657,8 +1678,8 @@
           </cell>
         </row>
         <row r="46">
-          <cell r="C46" t="str">
-            <v>Gas CCGT CCS</v>
+          <cell r="D46" t="str">
+            <v>gasCCGTCCS</v>
           </cell>
           <cell r="S46">
             <v>3.2</v>
@@ -1671,8 +1692,8 @@
           </cell>
         </row>
         <row r="48">
-          <cell r="C48" t="str">
-            <v>Nuclear</v>
+          <cell r="D48" t="str">
+            <v>nuclear</v>
           </cell>
           <cell r="S48">
             <v>3</v>
@@ -1685,8 +1706,8 @@
           </cell>
         </row>
         <row r="49">
-          <cell r="C49" t="str">
-            <v>Nuclear-flex</v>
+          <cell r="D49" t="str">
+            <v>nuclearFlexible</v>
           </cell>
           <cell r="S49">
             <v>3.1</v>
@@ -1699,8 +1720,8 @@
           </cell>
         </row>
         <row r="51">
-          <cell r="C51" t="str">
-            <v>Industry renewable CHP</v>
+          <cell r="D51" t="str">
+            <v>bioCHPIndustry</v>
           </cell>
           <cell r="S51">
             <v>2</v>
@@ -1713,8 +1734,8 @@
           </cell>
         </row>
         <row r="52">
-          <cell r="C52" t="str">
-            <v>Industry non-renewable CHP</v>
+          <cell r="D52" t="str">
+            <v>coalCHPIndustry</v>
           </cell>
           <cell r="S52">
             <v>2</v>
@@ -1727,8 +1748,8 @@
           </cell>
         </row>
         <row r="53">
-          <cell r="C53" t="str">
-            <v>Industry gas CHP</v>
+          <cell r="D53" t="str">
+            <v>gasCHPIndustry</v>
           </cell>
           <cell r="S53">
             <v>2</v>
@@ -1741,53 +1762,53 @@
           </cell>
         </row>
         <row r="55">
-          <cell r="C55" t="str">
-            <v>Battery discharger 4h</v>
+          <cell r="D55" t="str">
+            <v>BatteryCharger</v>
           </cell>
           <cell r="S55">
-            <v>1.6</v>
+            <v>1.4</v>
           </cell>
         </row>
         <row r="56">
-          <cell r="C56" t="str">
-            <v>Battery discharger</v>
+          <cell r="D56" t="str">
+            <v>BatteryDisch</v>
           </cell>
           <cell r="S56">
             <v>1.4</v>
           </cell>
         </row>
         <row r="57">
-          <cell r="C57" t="str">
-            <v>Battery charger 4h</v>
+          <cell r="D57" t="str">
+            <v>BatteryCharger4h</v>
           </cell>
           <cell r="S57">
             <v>1.6</v>
           </cell>
         </row>
         <row r="58">
-          <cell r="C58" t="str">
-            <v>Battery charger</v>
+          <cell r="D58" t="str">
+            <v>BatteryDisch4h</v>
           </cell>
           <cell r="S58">
-            <v>1.4</v>
+            <v>1.6</v>
           </cell>
         </row>
         <row r="60">
-          <cell r="C60" t="str">
-            <v>Solar Thermal</v>
+          <cell r="D60" t="str">
+            <v>solarThermal</v>
           </cell>
         </row>
         <row r="61">
-          <cell r="C61" t="str">
-            <v>Ground source heat pump</v>
+          <cell r="D61" t="str">
+            <v>GSHP</v>
           </cell>
           <cell r="S61">
             <v>6</v>
           </cell>
         </row>
         <row r="62">
-          <cell r="C62" t="str">
-            <v>Waste HOB</v>
+          <cell r="D62" t="str">
+            <v>wasteHOB</v>
           </cell>
           <cell r="S62">
             <v>2</v>
@@ -1800,8 +1821,8 @@
           </cell>
         </row>
         <row r="63">
-          <cell r="C63" t="str">
-            <v>Oil HOB</v>
+          <cell r="D63" t="str">
+            <v>oilHOB</v>
           </cell>
           <cell r="S63">
             <v>2</v>
@@ -1814,8 +1835,8 @@
           </cell>
         </row>
         <row r="64">
-          <cell r="C64" t="str">
-            <v>Gas HOB</v>
+          <cell r="D64" t="str">
+            <v>gasHOB</v>
           </cell>
           <cell r="S64">
             <v>2</v>
@@ -1828,8 +1849,8 @@
           </cell>
         </row>
         <row r="65">
-          <cell r="C65" t="str">
-            <v>Bio HOB</v>
+          <cell r="D65" t="str">
+            <v>bioHOB</v>
           </cell>
           <cell r="S65">
             <v>2</v>
@@ -1842,16 +1863,16 @@
           </cell>
         </row>
         <row r="66">
-          <cell r="C66" t="str">
-            <v>Electric boiler</v>
+          <cell r="D66" t="str">
+            <v>elecHOB</v>
           </cell>
           <cell r="S66">
-            <v>13</v>
+            <v>1.5</v>
           </cell>
         </row>
         <row r="67">
-          <cell r="C67" t="str">
-            <v>Waste CHP</v>
+          <cell r="D67" t="str">
+            <v>wasteCHP</v>
           </cell>
           <cell r="S67">
             <v>2</v>
@@ -1864,8 +1885,8 @@
           </cell>
         </row>
         <row r="68">
-          <cell r="C68" t="str">
-            <v>Coal CHP</v>
+          <cell r="D68" t="str">
+            <v>coalCHP</v>
           </cell>
           <cell r="S68">
             <v>2</v>
@@ -1878,8 +1899,8 @@
           </cell>
         </row>
         <row r="69">
-          <cell r="C69" t="str">
-            <v>Bio CHP</v>
+          <cell r="D69" t="str">
+            <v>bioCHP</v>
           </cell>
           <cell r="S69">
             <v>2</v>
@@ -1892,8 +1913,8 @@
           </cell>
         </row>
         <row r="70">
-          <cell r="C70" t="str">
-            <v>Gas CCGT CHP</v>
+          <cell r="D70" t="str">
+            <v>gasCCGTCHP</v>
           </cell>
           <cell r="S70">
             <v>1.6</v>
@@ -1906,16 +1927,16 @@
           </cell>
         </row>
         <row r="71">
-          <cell r="C71" t="str">
-            <v>Coal HOB</v>
+          <cell r="D71" t="str">
+            <v>coalHOB</v>
           </cell>
           <cell r="S71">
             <v>2</v>
           </cell>
         </row>
         <row r="72">
-          <cell r="C72" t="str">
-            <v>Coal CHP extraction</v>
+          <cell r="D72" t="str">
+            <v>coalCHPExtraction</v>
           </cell>
           <cell r="S72">
             <v>2</v>
@@ -1928,8 +1949,8 @@
           </cell>
         </row>
         <row r="73">
-          <cell r="C73" t="str">
-            <v>Bio CHP extraction</v>
+          <cell r="D73" t="str">
+            <v>bioCHPExtraction</v>
           </cell>
           <cell r="S73">
             <v>2</v>
@@ -1942,8 +1963,8 @@
           </cell>
         </row>
         <row r="74">
-          <cell r="C74" t="str">
-            <v>Gas CHP extraction</v>
+          <cell r="D74" t="str">
+            <v>gasCHPExtraction</v>
           </cell>
           <cell r="S74">
             <v>1.6</v>
@@ -1956,8 +1977,8 @@
           </cell>
         </row>
         <row r="75">
-          <cell r="C75" t="str">
-            <v>Oil shale CHP</v>
+          <cell r="D75" t="str">
+            <v>oilshaleCHP</v>
           </cell>
           <cell r="S75">
             <v>3.3</v>
@@ -1970,8 +1991,8 @@
           </cell>
         </row>
         <row r="76">
-          <cell r="C76" t="str">
-            <v>Gas OCGT CHP</v>
+          <cell r="D76" t="str">
+            <v>gasOCGTCHP</v>
           </cell>
           <cell r="S76">
             <v>1.6</v>
@@ -1984,89 +2005,89 @@
           </cell>
         </row>
         <row r="77">
-          <cell r="C77" t="str">
-            <v>Heat storage discharger</v>
+          <cell r="D77" t="str">
+            <v>HeatStorageCharger</v>
           </cell>
           <cell r="S77">
             <v>1.4</v>
           </cell>
         </row>
         <row r="78">
-          <cell r="C78" t="str">
-            <v>Heat storage charger</v>
+          <cell r="D78" t="str">
+            <v>HeatStorageDisch</v>
           </cell>
           <cell r="S78">
             <v>1.4</v>
           </cell>
         </row>
         <row r="79">
-          <cell r="C79" t="str">
-            <v>Large heat storage discharger</v>
+          <cell r="D79" t="str">
+            <v>heatStorageChargerLarge</v>
           </cell>
           <cell r="S79">
             <v>1.7</v>
           </cell>
         </row>
         <row r="80">
-          <cell r="C80" t="str">
-            <v>Large heat storage charger</v>
+          <cell r="D80" t="str">
+            <v>heatStorageDischLarge</v>
           </cell>
           <cell r="S80">
             <v>1.7</v>
           </cell>
         </row>
         <row r="81">
-          <cell r="C81" t="str">
-            <v>Seasonal heat storage discharger</v>
+          <cell r="D81" t="str">
+            <v>heatStorageChargerSeasonal</v>
           </cell>
           <cell r="S81">
             <v>2</v>
           </cell>
         </row>
         <row r="82">
-          <cell r="C82" t="str">
-            <v>Seasonal heat storage charger</v>
+          <cell r="D82" t="str">
+            <v>heatStorageDischSeasonal</v>
           </cell>
           <cell r="S82">
             <v>2</v>
           </cell>
         </row>
         <row r="84">
-          <cell r="C84" t="str">
-            <v>DR upwards 2</v>
+          <cell r="D84" t="str">
+            <v>DRupwards2</v>
           </cell>
         </row>
         <row r="85">
-          <cell r="C85" t="str">
-            <v>DR upwards 1</v>
+          <cell r="D85" t="str">
+            <v>DRupwards1</v>
           </cell>
         </row>
         <row r="86">
-          <cell r="C86" t="str">
-            <v>DR cutoff tier 3</v>
+          <cell r="D86" t="str">
+            <v>DRcutofftier3</v>
           </cell>
           <cell r="S86">
             <v>2000</v>
           </cell>
         </row>
         <row r="87">
-          <cell r="C87" t="str">
-            <v>DR cutoff tier 2</v>
+          <cell r="D87" t="str">
+            <v>DRcutofftier2</v>
           </cell>
           <cell r="S87">
             <v>1000</v>
           </cell>
         </row>
         <row r="88">
-          <cell r="C88" t="str">
-            <v>DR cutoff tier 1</v>
+          <cell r="D88" t="str">
+            <v>DRcutofftier1</v>
           </cell>
           <cell r="S88">
             <v>400</v>
           </cell>
         </row>
         <row r="90">
-          <cell r="C90" t="str">
+          <cell r="D90" t="str">
             <v>Electrolyser</v>
           </cell>
           <cell r="S90">
@@ -2080,8 +2101,8 @@
           </cell>
         </row>
         <row r="91">
-          <cell r="C91" t="str">
-            <v>Electrolyser-SOEC</v>
+          <cell r="D91" t="str">
+            <v>ElectrolyserSOEC</v>
           </cell>
           <cell r="S91">
             <v>1.5</v>
@@ -2094,8 +2115,8 @@
           </cell>
         </row>
         <row r="92">
-          <cell r="C92" t="str">
-            <v>Hydrogen OCGT</v>
+          <cell r="D92" t="str">
+            <v>hydrogenOCGT</v>
           </cell>
           <cell r="S92">
             <v>5</v>
@@ -2105,24 +2126,24 @@
           </cell>
         </row>
         <row r="93">
-          <cell r="C93" t="str">
-            <v>Short-term hydrogen storage discharger</v>
+          <cell r="D93" t="str">
+            <v>H2StorageDisch</v>
           </cell>
           <cell r="S93">
             <v>1.5</v>
           </cell>
         </row>
         <row r="94">
-          <cell r="C94" t="str">
-            <v>Short-term hydrogen storage charger</v>
+          <cell r="D94" t="str">
+            <v>H2StorageCharger</v>
           </cell>
           <cell r="S94">
             <v>1.5</v>
           </cell>
         </row>
         <row r="95">
-          <cell r="C95" t="str">
-            <v>Long-term hydrogen storage discharger</v>
+          <cell r="D95" t="str">
+            <v>H2StorageDischLongterm</v>
           </cell>
           <cell r="S95">
             <v>2</v>
@@ -2132,8 +2153,8 @@
           </cell>
         </row>
         <row r="96">
-          <cell r="C96" t="str">
-            <v>Long-term hydrogen storage charger</v>
+          <cell r="D96" t="str">
+            <v>H2StorageChargerLongterm</v>
           </cell>
           <cell r="S96">
             <v>2</v>
@@ -2454,37 +2475,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="K1" s="31" t="s">
         <v>39</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K1" s="31" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -2492,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D2" s="6">
         <v>1</v>
@@ -2518,13 +2539,13 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D3" s="6">
         <v>1</v>
@@ -2547,13 +2568,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D4" s="6">
         <v>1</v>
@@ -2576,13 +2597,13 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D5" s="6">
         <v>1</v>
@@ -2605,13 +2626,13 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
@@ -2634,13 +2655,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D7" s="6">
         <v>1</v>
@@ -2663,13 +2684,13 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D8" s="6">
         <v>1</v>
@@ -2692,13 +2713,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
@@ -2721,13 +2742,13 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D10" s="6">
         <v>1</v>
@@ -2750,13 +2771,13 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D11" s="6">
         <v>1</v>
@@ -2779,13 +2800,13 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D12" s="6">
         <v>1</v>
@@ -2811,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D13" s="6">
         <v>1</v>
@@ -2837,13 +2858,13 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
@@ -2866,13 +2887,13 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
@@ -2895,13 +2916,13 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D16" s="6">
         <v>1</v>
@@ -2924,13 +2945,13 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D17" s="6">
         <v>1</v>
@@ -2953,13 +2974,13 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D18" s="6">
         <v>1</v>
@@ -2982,13 +3003,13 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
@@ -3011,13 +3032,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D20" s="6">
         <v>1</v>
@@ -3040,13 +3061,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -3066,18 +3087,18 @@
       </c>
       <c r="J21" s="12"/>
       <c r="K21" s="32" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -3100,13 +3121,13 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
@@ -3132,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D24" s="6">
         <v>1</v>
@@ -3158,13 +3179,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D25" s="6">
         <v>1</v>
@@ -3176,19 +3197,19 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K25" s="12"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D26" s="6">
         <v>1</v>
@@ -3211,13 +3232,13 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D27" s="6">
         <v>1</v>
@@ -3240,13 +3261,13 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D28" s="6">
         <v>1</v>
@@ -3269,13 +3290,13 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D29" s="6">
         <v>1</v>
@@ -3298,13 +3319,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="13" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D30" s="6">
         <v>1</v>
@@ -3324,18 +3345,18 @@
       </c>
       <c r="J30" s="12"/>
       <c r="K30" s="32" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D31" s="6">
         <v>1</v>
@@ -3355,18 +3376,18 @@
       </c>
       <c r="J31" s="12"/>
       <c r="K31" s="32" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D32" s="6">
         <v>1</v>
@@ -3392,10 +3413,10 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D33" s="6">
         <v>1</v>
@@ -3407,19 +3428,19 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="K33" s="12"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="13" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D34" s="6">
         <v>1</v>
@@ -3440,13 +3461,13 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D35" s="6">
         <v>1</v>
@@ -3467,13 +3488,13 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="13" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D36" s="6">
         <v>1</v>
@@ -3494,13 +3515,13 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D37" s="6">
         <v>1</v>
@@ -3521,13 +3542,13 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D38" s="6">
         <v>1</v>
@@ -3548,13 +3569,13 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D39" s="6">
         <v>1</v>
@@ -3575,13 +3596,13 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D40" s="6">
         <v>1</v>
@@ -3602,13 +3623,13 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D41" s="6">
         <v>1</v>
@@ -3644,7 +3665,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
@@ -3653,62 +3674,63 @@
     <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H1" s="30" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="O1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="P1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="Q1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="R1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="S1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="T1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="U1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="V1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
@@ -3716,10 +3738,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -3732,23 +3754,23 @@
         <v>2.2599999999999998</v>
       </c>
       <c r="G2">
-        <f t="shared" ref="G2:H2" si="0">ROUND(SUMIFS(S$31:S$36,$Q$31:$Q$36,$B2) * (1 + SUMIFS($U$7:$U$28,$Q$7:$Q$28,$A2)), 2)</f>
+        <f t="shared" ref="G2:G59" si="0">ROUND(SUMIFS(S$31:S$36,$Q$31:$Q$36,$B2) * (1 + SUMIFS($U$7:$U$28,$Q$7:$Q$28,$A2)), 2)</f>
         <v>6.2</v>
       </c>
       <c r="H2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="H2:H59" si="1">ROUND(SUMIFS(T$31:T$36,$Q$31:$Q$36,$B2) * (1 + SUMIFS($U$7:$U$28,$Q$7:$Q$28,$A2)), 2)</f>
         <v>6.2</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -3757,27 +3779,27 @@
         <v>113.94</v>
       </c>
       <c r="F3">
-        <f t="shared" ref="F3:F59" si="1">ROUND(SUMIFS(R$31:R$36,$Q$31:$Q$36,$B3) * (1 + SUMIFS($U$7:$U$28,$Q$7:$Q$28,$A3)), 2)</f>
+        <f t="shared" ref="F3:F59" si="2">ROUND(SUMIFS(R$31:R$36,$Q$31:$Q$36,$B3) * (1 + SUMIFS($U$7:$U$28,$Q$7:$Q$28,$A3)), 2)</f>
         <v>2.2400000000000002</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G59" si="2">ROUND(SUMIFS(S$31:S$36,$Q$31:$Q$36,$B3) * (1 + SUMIFS($U$7:$U$28,$Q$7:$Q$28,$A3)), 2)</f>
+        <f t="shared" si="0"/>
         <v>6.17</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H59" si="3">ROUND(SUMIFS(T$31:T$36,$Q$31:$Q$36,$B3) * (1 + SUMIFS($U$7:$U$28,$Q$7:$Q$28,$A3)), 2)</f>
+        <f t="shared" si="1"/>
         <v>6.17</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -3786,27 +3808,27 @@
         <v>4031</v>
       </c>
       <c r="F4">
+        <f t="shared" si="2"/>
+        <v>2.91</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>8.01</v>
+      </c>
+      <c r="H4">
         <f t="shared" si="1"/>
-        <v>2.91</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="2"/>
-        <v>8.01</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="3"/>
         <v>8.01</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -3815,27 +3837,27 @@
         <v>4036</v>
       </c>
       <c r="F5">
+        <f t="shared" si="2"/>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>6.09</v>
+      </c>
+      <c r="H5">
         <f t="shared" si="1"/>
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="2"/>
-        <v>6.09</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="3"/>
         <v>6.09</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -3844,39 +3866,39 @@
         <v>3300</v>
       </c>
       <c r="F6">
+        <f t="shared" si="2"/>
+        <v>1.83</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>5.04</v>
+      </c>
+      <c r="H6">
         <f t="shared" si="1"/>
-        <v>1.83</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="2"/>
         <v>5.04</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="3"/>
-        <v>5.04</v>
-      </c>
       <c r="R6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="S6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="T6" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="U6" s="27" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -3885,15 +3907,15 @@
         <v>20500</v>
       </c>
       <c r="F7">
+        <f t="shared" si="2"/>
+        <v>2.11</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>5.8</v>
+      </c>
+      <c r="H7">
         <f t="shared" si="1"/>
-        <v>2.11</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="2"/>
-        <v>5.8</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="3"/>
         <v>5.8</v>
       </c>
       <c r="Q7" s="5" t="s">
@@ -3918,13 +3940,13 @@
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -3933,19 +3955,19 @@
         <v>128</v>
       </c>
       <c r="F8">
+        <f t="shared" si="2"/>
+        <v>1.53</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>4.22</v>
+      </c>
+      <c r="H8">
         <f t="shared" si="1"/>
-        <v>1.53</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="2"/>
         <v>4.22</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="3"/>
-        <v>4.22</v>
-      </c>
       <c r="Q8" s="5" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="R8" s="6">
         <f>'[1]vomcost mult'!O12</f>
@@ -3966,13 +3988,13 @@
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -3981,19 +4003,19 @@
         <v>1557</v>
       </c>
       <c r="F9">
+        <f t="shared" si="2"/>
+        <v>1.4</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>3.86</v>
+      </c>
+      <c r="H9">
         <f t="shared" si="1"/>
-        <v>1.4</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="2"/>
         <v>3.86</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="3"/>
-        <v>3.86</v>
-      </c>
       <c r="Q9" s="5" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="R9" s="6">
         <f>'[1]vomcost mult'!O13</f>
@@ -4014,13 +4036,13 @@
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -4029,19 +4051,19 @@
         <v>38</v>
       </c>
       <c r="F10">
+        <f t="shared" si="2"/>
+        <v>2.36</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>6.49</v>
+      </c>
+      <c r="H10">
         <f t="shared" si="1"/>
-        <v>2.36</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="2"/>
         <v>6.49</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="3"/>
-        <v>6.49</v>
-      </c>
       <c r="Q10" s="5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R10" s="6">
         <f>'[1]vomcost mult'!O14</f>
@@ -4062,13 +4084,13 @@
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -4077,19 +4099,19 @@
         <v>506.5</v>
       </c>
       <c r="F11">
+        <f t="shared" si="2"/>
+        <v>1.38</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+      <c r="H11">
         <f t="shared" si="1"/>
-        <v>1.38</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="2"/>
         <v>3.8</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="3"/>
-        <v>3.8</v>
-      </c>
       <c r="Q11" s="5" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="R11" s="6">
         <f>'[1]vomcost mult'!O15</f>
@@ -4110,13 +4132,13 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -4125,19 +4147,19 @@
         <v>1826</v>
       </c>
       <c r="F12">
+        <f t="shared" si="2"/>
+        <v>2.33</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>6.41</v>
+      </c>
+      <c r="H12">
         <f t="shared" si="1"/>
-        <v>2.33</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="2"/>
         <v>6.41</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="3"/>
-        <v>6.41</v>
-      </c>
       <c r="Q12" s="5" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="R12" s="6">
         <f>'[1]vomcost mult'!O16</f>
@@ -4161,10 +4183,10 @@
         <v>0</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -4173,19 +4195,19 @@
         <v>2429.5540000000001</v>
       </c>
       <c r="F13">
+        <f t="shared" si="2"/>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>5.64</v>
+      </c>
+      <c r="H13">
         <f t="shared" si="1"/>
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="2"/>
         <v>5.64</v>
       </c>
-      <c r="H13">
-        <f t="shared" si="3"/>
-        <v>5.64</v>
-      </c>
       <c r="Q13" s="5" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="R13" s="6">
         <f>'[1]vomcost mult'!O17</f>
@@ -4206,13 +4228,13 @@
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -4221,19 +4243,19 @@
         <v>8152</v>
       </c>
       <c r="F14">
+        <f t="shared" si="2"/>
+        <v>2.62</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>7.28</v>
+      </c>
+      <c r="H14">
         <f t="shared" si="1"/>
-        <v>2.62</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="2"/>
         <v>7.28</v>
       </c>
-      <c r="H14">
-        <f t="shared" si="3"/>
-        <v>7.28</v>
-      </c>
       <c r="Q14" s="5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R14" s="6">
         <f>'[1]vomcost mult'!O18</f>
@@ -4254,13 +4276,13 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -4269,19 +4291,19 @@
         <v>1297</v>
       </c>
       <c r="F15">
+        <f t="shared" si="2"/>
+        <v>1.99</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>5.54</v>
+      </c>
+      <c r="H15">
         <f t="shared" si="1"/>
-        <v>1.99</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="2"/>
         <v>5.54</v>
       </c>
-      <c r="H15">
-        <f t="shared" si="3"/>
-        <v>5.54</v>
-      </c>
       <c r="Q15" s="5" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="R15" s="6">
         <f>'[1]vomcost mult'!O19</f>
@@ -4302,13 +4324,13 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -4317,19 +4339,19 @@
         <v>10970</v>
       </c>
       <c r="F16">
+        <f t="shared" si="2"/>
+        <v>1.65</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>4.59</v>
+      </c>
+      <c r="H16">
         <f t="shared" si="1"/>
-        <v>1.65</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="2"/>
         <v>4.59</v>
       </c>
-      <c r="H16">
-        <f t="shared" si="3"/>
-        <v>4.59</v>
-      </c>
       <c r="Q16" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R16" s="6">
         <f>'[1]vomcost mult'!O20</f>
@@ -4350,13 +4372,13 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -4365,19 +4387,19 @@
         <v>3200</v>
       </c>
       <c r="F17">
+        <f t="shared" si="2"/>
+        <v>1.99</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>5.54</v>
+      </c>
+      <c r="H17">
         <f t="shared" si="1"/>
-        <v>1.99</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="2"/>
         <v>5.54</v>
       </c>
-      <c r="H17">
-        <f t="shared" si="3"/>
-        <v>5.54</v>
-      </c>
       <c r="Q17" s="5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R17" s="6">
         <f>'[1]vomcost mult'!O21</f>
@@ -4398,13 +4420,13 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -4413,19 +4435,19 @@
         <v>8477</v>
       </c>
       <c r="F18">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>5.27</v>
+      </c>
+      <c r="H18">
         <f t="shared" si="1"/>
-        <v>1.9</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="2"/>
         <v>5.27</v>
       </c>
-      <c r="H18">
-        <f t="shared" si="3"/>
-        <v>5.27</v>
-      </c>
       <c r="Q18" s="5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R18" s="6">
         <f>'[1]vomcost mult'!O22</f>
@@ -4446,13 +4468,13 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -4461,19 +4483,19 @@
         <v>183.8</v>
       </c>
       <c r="F19">
+        <f t="shared" si="2"/>
+        <v>1.24</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>3.45</v>
+      </c>
+      <c r="H19">
         <f t="shared" si="1"/>
-        <v>1.24</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="2"/>
         <v>3.45</v>
       </c>
-      <c r="H19">
-        <f t="shared" si="3"/>
-        <v>3.45</v>
-      </c>
       <c r="Q19" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="R19" s="6">
         <f>'[1]vomcost mult'!O23</f>
@@ -4494,13 +4516,13 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -4509,19 +4531,19 @@
         <v>5315</v>
       </c>
       <c r="F20">
+        <f t="shared" si="2"/>
+        <v>2.13</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>5.91</v>
+      </c>
+      <c r="H20">
         <f t="shared" si="1"/>
-        <v>2.13</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="2"/>
         <v>5.91</v>
       </c>
-      <c r="H20">
-        <f t="shared" si="3"/>
-        <v>5.91</v>
-      </c>
       <c r="Q20" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="R20" s="6">
         <f>'[1]vomcost mult'!O24</f>
@@ -4542,13 +4564,13 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -4557,19 +4579,19 @@
         <v>8055</v>
       </c>
       <c r="F21">
+        <f t="shared" si="2"/>
+        <v>2.11</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>5.87</v>
+      </c>
+      <c r="H21">
         <f t="shared" si="1"/>
-        <v>2.11</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="2"/>
         <v>5.87</v>
       </c>
-      <c r="H21">
-        <f t="shared" si="3"/>
-        <v>5.87</v>
-      </c>
       <c r="Q21" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R21" s="6">
         <f>'[1]vomcost mult'!O25</f>
@@ -4590,13 +4612,13 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -4605,19 +4627,19 @@
         <v>2331</v>
       </c>
       <c r="F22">
+        <f t="shared" si="2"/>
+        <v>2.1</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>5.83</v>
+      </c>
+      <c r="H22">
         <f t="shared" si="1"/>
-        <v>2.1</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="2"/>
         <v>5.83</v>
       </c>
-      <c r="H22">
-        <f t="shared" si="3"/>
-        <v>5.83</v>
-      </c>
       <c r="Q22" s="5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="R22" s="6">
         <f>'[1]vomcost mult'!O26</f>
@@ -4638,13 +4660,13 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -4653,19 +4675,19 @@
         <v>237</v>
       </c>
       <c r="F23">
+        <f t="shared" si="2"/>
+        <v>2.08</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>5.79</v>
+      </c>
+      <c r="H23">
         <f t="shared" si="1"/>
-        <v>2.08</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="2"/>
         <v>5.79</v>
       </c>
-      <c r="H23">
-        <f t="shared" si="3"/>
-        <v>5.79</v>
-      </c>
       <c r="Q23" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="R23" s="6">
         <f>'[1]vomcost mult'!O27</f>
@@ -4689,10 +4711,10 @@
         <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -4701,19 +4723,19 @@
         <v>3459.28</v>
       </c>
       <c r="F24">
+        <f t="shared" si="2"/>
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>4.51</v>
+      </c>
+      <c r="H24">
         <f t="shared" si="1"/>
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="2"/>
         <v>4.51</v>
       </c>
-      <c r="H24">
-        <f t="shared" si="3"/>
-        <v>4.51</v>
-      </c>
       <c r="Q24" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="R24" s="6">
         <f>'[1]vomcost mult'!O28</f>
@@ -4734,34 +4756,34 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="F25">
+        <f t="shared" si="2"/>
+        <v>2.91</v>
+      </c>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>5.82</v>
+      </c>
+      <c r="H25">
         <f t="shared" si="1"/>
-        <v>2.91</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="2"/>
         <v>5.82</v>
       </c>
-      <c r="H25">
-        <f t="shared" si="3"/>
-        <v>5.82</v>
-      </c>
       <c r="J25" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Q25" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="R25" s="6">
         <f>'[1]vomcost mult'!O29</f>
@@ -4782,13 +4804,13 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -4797,19 +4819,19 @@
         <v>1644</v>
       </c>
       <c r="F26">
+        <f t="shared" si="2"/>
+        <v>2.2200000000000002</v>
+      </c>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>4.43</v>
+      </c>
+      <c r="H26">
         <f t="shared" si="1"/>
-        <v>2.2200000000000002</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="2"/>
         <v>4.43</v>
       </c>
-      <c r="H26">
-        <f t="shared" si="3"/>
-        <v>4.43</v>
-      </c>
       <c r="Q26" s="5" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="R26" s="6">
         <f>'[1]vomcost mult'!O30</f>
@@ -4830,13 +4852,13 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -4845,19 +4867,19 @@
         <v>2683</v>
       </c>
       <c r="F27">
+        <f t="shared" si="2"/>
+        <v>1.83</v>
+      </c>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>3.67</v>
+      </c>
+      <c r="H27">
         <f t="shared" si="1"/>
-        <v>1.83</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="2"/>
         <v>3.67</v>
       </c>
-      <c r="H27">
-        <f t="shared" si="3"/>
-        <v>3.67</v>
-      </c>
       <c r="Q27" s="5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="R27" s="6">
         <f>'[1]vomcost mult'!O31</f>
@@ -4878,13 +4900,13 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D28">
         <v>1</v>
@@ -4893,19 +4915,19 @@
         <v>1850</v>
       </c>
       <c r="F28">
+        <f t="shared" si="2"/>
+        <v>2.11</v>
+      </c>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>4.22</v>
+      </c>
+      <c r="H28">
         <f t="shared" si="1"/>
-        <v>2.11</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="2"/>
         <v>4.22</v>
       </c>
-      <c r="H28">
-        <f t="shared" si="3"/>
-        <v>4.22</v>
-      </c>
       <c r="Q28" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="R28" s="6">
         <f>'[1]vomcost mult'!O32</f>
@@ -4926,13 +4948,13 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C29" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -4941,27 +4963,27 @@
         <v>4631.3999999999996</v>
       </c>
       <c r="F29">
+        <f t="shared" si="2"/>
+        <v>2.62</v>
+      </c>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>5.24</v>
+      </c>
+      <c r="H29">
         <f t="shared" si="1"/>
-        <v>2.62</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="2"/>
-        <v>5.24</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="3"/>
         <v>5.24</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -4970,36 +4992,36 @@
         <v>5540.4</v>
       </c>
       <c r="F30">
+        <f t="shared" si="2"/>
+        <v>2.65</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>5.3</v>
+      </c>
+      <c r="H30">
         <f t="shared" si="1"/>
-        <v>2.65</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="2"/>
         <v>5.3</v>
       </c>
-      <c r="H30">
-        <f t="shared" si="3"/>
-        <v>5.3</v>
-      </c>
       <c r="R30" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="S30" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="T30" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C31" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -5008,42 +5030,42 @@
         <v>23605.1</v>
       </c>
       <c r="F31">
+        <f t="shared" si="2"/>
+        <v>2.59</v>
+      </c>
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>5.18</v>
+      </c>
+      <c r="H31">
         <f t="shared" si="1"/>
-        <v>2.59</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="2"/>
         <v>5.18</v>
       </c>
-      <c r="H31">
-        <f t="shared" si="3"/>
-        <v>5.18</v>
-      </c>
       <c r="Q31" t="s">
-        <v>6</v>
+        <v>108</v>
       </c>
       <c r="R31">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$C:$C, $Q31)</f>
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $Q31)</f>
         <v>2</v>
       </c>
       <c r="S31">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$C:$C, $Q31)</f>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $Q31)</f>
         <v>5.5</v>
       </c>
       <c r="T31">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$C:$C, $Q31)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $Q31)</f>
         <v>5.5</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>4</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -5052,30 +5074,30 @@
         <v>178.8</v>
       </c>
       <c r="F32">
+        <f t="shared" si="2"/>
+        <v>1.38</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>2.76</v>
+      </c>
+      <c r="H32">
         <f t="shared" si="1"/>
-        <v>1.38</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="2"/>
         <v>2.76</v>
       </c>
-      <c r="H32">
-        <f t="shared" si="3"/>
-        <v>2.76</v>
-      </c>
       <c r="Q32" t="s">
+        <v>109</v>
+      </c>
+      <c r="R32">
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $Q32)</f>
+        <v>1.8</v>
+      </c>
+      <c r="S32">
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $Q32)</f>
         <v>5</v>
       </c>
-      <c r="R32">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$C:$C, $Q32)</f>
-        <v>1.8</v>
-      </c>
-      <c r="S32">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$C:$C, $Q32)</f>
-        <v>5</v>
-      </c>
       <c r="T32">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$C:$C, $Q32)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $Q32)</f>
         <v>5</v>
       </c>
     </row>
@@ -5084,10 +5106,10 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -5096,86 +5118,86 @@
         <v>2560</v>
       </c>
       <c r="F33">
+        <f t="shared" si="2"/>
+        <v>1.8</v>
+      </c>
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>3.95</v>
+      </c>
+      <c r="H33">
         <f t="shared" si="1"/>
-        <v>1.8</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="2"/>
         <v>3.95</v>
       </c>
-      <c r="H33">
-        <f t="shared" si="3"/>
-        <v>3.95</v>
-      </c>
       <c r="Q33" t="s">
+        <v>110</v>
+      </c>
+      <c r="R33">
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $Q33)</f>
+        <v>2</v>
+      </c>
+      <c r="S33">
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $Q33)</f>
         <v>4</v>
       </c>
-      <c r="R33">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$C:$C, $Q33)</f>
-        <v>2</v>
-      </c>
-      <c r="S33">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$C:$C, $Q33)</f>
-        <v>4</v>
-      </c>
       <c r="T33">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$C:$C, $Q33)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $Q33)</f>
         <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C34" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D34">
         <v>1</v>
       </c>
       <c r="F34">
+        <f t="shared" si="2"/>
+        <v>2.33</v>
+      </c>
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H34">
         <f t="shared" si="1"/>
-        <v>2.33</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="2"/>
         <v>5.0999999999999996</v>
       </c>
-      <c r="H34">
-        <f t="shared" si="3"/>
-        <v>5.0999999999999996</v>
-      </c>
       <c r="J34" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Q34" t="s">
-        <v>3</v>
+        <v>111</v>
       </c>
       <c r="R34">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$C:$C, $Q34)</f>
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $Q34)</f>
         <v>1.6</v>
       </c>
       <c r="S34">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$C:$C, $Q34)</f>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $Q34)</f>
         <v>3.5</v>
       </c>
       <c r="T34">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$C:$C, $Q34)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $Q34)</f>
         <v>3.5</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C35" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -5184,42 +5206,42 @@
         <v>1361</v>
       </c>
       <c r="F35">
+        <f t="shared" si="2"/>
+        <v>1.77</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>3.88</v>
+      </c>
+      <c r="H35">
         <f t="shared" si="1"/>
-        <v>1.77</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="2"/>
         <v>3.88</v>
       </c>
-      <c r="H35">
-        <f t="shared" si="3"/>
-        <v>3.88</v>
-      </c>
       <c r="Q35" t="s">
-        <v>2</v>
+        <v>112</v>
       </c>
       <c r="R35">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$C:$C, $Q35)</f>
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $Q35)</f>
         <v>1.8</v>
       </c>
       <c r="S35">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$C:$C, $Q35)</f>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $Q35)</f>
         <v>3.1</v>
       </c>
       <c r="T35">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$C:$C, $Q35)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $Q35)</f>
         <v>3.1</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B36" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C36" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -5228,42 +5250,42 @@
         <v>2424</v>
       </c>
       <c r="F36">
+        <f t="shared" si="2"/>
+        <v>1.47</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>3.21</v>
+      </c>
+      <c r="H36">
         <f t="shared" si="1"/>
-        <v>1.47</v>
-      </c>
-      <c r="G36">
-        <f t="shared" si="2"/>
         <v>3.21</v>
       </c>
-      <c r="H36">
-        <f t="shared" si="3"/>
-        <v>3.21</v>
-      </c>
       <c r="Q36" t="s">
-        <v>1</v>
+        <v>113</v>
       </c>
       <c r="R36">
-        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$C:$C, $Q36)</f>
+        <f>SUMIFS([2]unittypedata!$S:$S,[2]unittypedata!$D:$D, $Q36)</f>
         <v>1.4</v>
       </c>
       <c r="S36">
-        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$C:$C, $Q36)</f>
+        <f>SUMIFS([2]unittypedata!$Y:$Y,[2]unittypedata!$D:$D, $Q36)</f>
         <v>3</v>
       </c>
       <c r="T36">
-        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$C:$C, $Q36)</f>
+        <f>SUMIFS([2]unittypedata!$Z:$Z,[2]unittypedata!$D:$D, $Q36)</f>
         <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -5272,27 +5294,27 @@
         <v>1850</v>
       </c>
       <c r="F37">
+        <f t="shared" si="2"/>
+        <v>1.69</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>3.69</v>
+      </c>
+      <c r="H37">
         <f t="shared" si="1"/>
-        <v>1.69</v>
-      </c>
-      <c r="G37">
-        <f t="shared" si="2"/>
-        <v>3.69</v>
-      </c>
-      <c r="H37">
-        <f t="shared" si="3"/>
         <v>3.69</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C38" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -5301,56 +5323,56 @@
         <v>84</v>
       </c>
       <c r="F38">
+        <f t="shared" si="2"/>
+        <v>2.1</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>4.59</v>
+      </c>
+      <c r="H38">
         <f t="shared" si="1"/>
-        <v>2.1</v>
-      </c>
-      <c r="G38">
-        <f t="shared" si="2"/>
-        <v>4.59</v>
-      </c>
-      <c r="H38">
-        <f t="shared" si="3"/>
         <v>4.59</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B39" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D39">
         <v>1</v>
       </c>
       <c r="F39">
+        <f t="shared" si="2"/>
+        <v>2.12</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>4.6399999999999997</v>
+      </c>
+      <c r="H39">
         <f t="shared" si="1"/>
-        <v>2.12</v>
-      </c>
-      <c r="G39">
-        <f t="shared" si="2"/>
         <v>4.6399999999999997</v>
       </c>
-      <c r="H39">
-        <f t="shared" si="3"/>
-        <v>4.6399999999999997</v>
-      </c>
       <c r="J39" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C40" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -5359,27 +5381,27 @@
         <v>1030</v>
       </c>
       <c r="F40">
+        <f t="shared" si="2"/>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>4.54</v>
+      </c>
+      <c r="H40">
         <f t="shared" si="1"/>
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="G40">
-        <f t="shared" si="2"/>
-        <v>4.54</v>
-      </c>
-      <c r="H40">
-        <f t="shared" si="3"/>
         <v>4.54</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>3</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -5388,15 +5410,15 @@
         <v>172</v>
       </c>
       <c r="F41">
+        <f t="shared" si="2"/>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="0"/>
+        <v>2.42</v>
+      </c>
+      <c r="H41">
         <f t="shared" si="1"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="G41">
-        <f t="shared" si="2"/>
-        <v>2.42</v>
-      </c>
-      <c r="H41">
-        <f t="shared" si="3"/>
         <v>2.42</v>
       </c>
     </row>
@@ -5405,39 +5427,39 @@
         <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="F42">
+        <f t="shared" si="2"/>
+        <v>2.0299999999999998</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+      <c r="H42">
         <f t="shared" si="1"/>
-        <v>2.0299999999999998</v>
-      </c>
-      <c r="G42">
-        <f t="shared" si="2"/>
         <v>3.5</v>
       </c>
-      <c r="H42">
-        <f t="shared" si="3"/>
-        <v>3.5</v>
-      </c>
       <c r="J42" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C43" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -5446,27 +5468,27 @@
         <v>1308</v>
       </c>
       <c r="F43">
+        <f t="shared" si="2"/>
+        <v>2.02</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="0"/>
+        <v>3.48</v>
+      </c>
+      <c r="H43">
         <f t="shared" si="1"/>
-        <v>2.02</v>
-      </c>
-      <c r="G43">
-        <f t="shared" si="2"/>
-        <v>3.48</v>
-      </c>
-      <c r="H43">
-        <f t="shared" si="3"/>
         <v>3.48</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C44" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -5475,27 +5497,27 @@
         <v>3989</v>
       </c>
       <c r="F44">
+        <f t="shared" si="2"/>
+        <v>2.62</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="0"/>
+        <v>4.51</v>
+      </c>
+      <c r="H44">
         <f t="shared" si="1"/>
-        <v>2.62</v>
-      </c>
-      <c r="G44">
-        <f t="shared" si="2"/>
-        <v>4.51</v>
-      </c>
-      <c r="H44">
-        <f t="shared" si="3"/>
         <v>4.51</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -5504,27 +5526,27 @@
         <v>6056</v>
       </c>
       <c r="F45">
+        <f t="shared" si="2"/>
+        <v>1.99</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="0"/>
+        <v>3.43</v>
+      </c>
+      <c r="H45">
         <f t="shared" si="1"/>
-        <v>1.99</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="2"/>
-        <v>3.43</v>
-      </c>
-      <c r="H45">
-        <f t="shared" si="3"/>
         <v>3.43</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -5533,27 +5555,27 @@
         <v>3330</v>
       </c>
       <c r="F46">
+        <f t="shared" si="2"/>
+        <v>1.65</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="0"/>
+        <v>2.84</v>
+      </c>
+      <c r="H46">
         <f t="shared" si="1"/>
-        <v>1.65</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="2"/>
-        <v>2.84</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="3"/>
         <v>2.84</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -5562,27 +5584,27 @@
         <v>1950</v>
       </c>
       <c r="F47">
+        <f t="shared" si="2"/>
+        <v>1.9</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="0"/>
+        <v>3.27</v>
+      </c>
+      <c r="H47">
         <f t="shared" si="1"/>
-        <v>1.9</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="2"/>
-        <v>3.27</v>
-      </c>
-      <c r="H47">
-        <f t="shared" si="3"/>
         <v>3.27</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C48" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -5591,27 +5613,27 @@
         <v>900</v>
       </c>
       <c r="F48">
+        <f t="shared" si="2"/>
+        <v>1.38</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="0"/>
+        <v>2.38</v>
+      </c>
+      <c r="H48">
         <f t="shared" si="1"/>
-        <v>1.38</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="2"/>
-        <v>2.38</v>
-      </c>
-      <c r="H48">
-        <f t="shared" si="3"/>
         <v>2.38</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B49" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -5620,27 +5642,27 @@
         <v>1323</v>
       </c>
       <c r="F49">
+        <f t="shared" si="2"/>
+        <v>1.24</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="0"/>
+        <v>2.14</v>
+      </c>
+      <c r="H49">
         <f t="shared" si="1"/>
-        <v>1.24</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="2"/>
-        <v>2.14</v>
-      </c>
-      <c r="H49">
-        <f t="shared" si="3"/>
         <v>2.14</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B50" t="s">
-        <v>2</v>
+        <v>116</v>
       </c>
       <c r="C50" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -5649,15 +5671,15 @@
         <v>2744</v>
       </c>
       <c r="F50">
+        <f t="shared" si="2"/>
+        <v>2.1</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="0"/>
+        <v>3.61</v>
+      </c>
+      <c r="H50">
         <f t="shared" si="1"/>
-        <v>2.1</v>
-      </c>
-      <c r="G50">
-        <f t="shared" si="2"/>
-        <v>3.61</v>
-      </c>
-      <c r="H50">
-        <f t="shared" si="3"/>
         <v>3.61</v>
       </c>
     </row>
@@ -5666,39 +5688,39 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D51">
         <v>1</v>
       </c>
       <c r="F51">
+        <f t="shared" si="2"/>
+        <v>1.58</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="0"/>
+        <v>3.38</v>
+      </c>
+      <c r="H51">
         <f t="shared" si="1"/>
-        <v>1.58</v>
-      </c>
-      <c r="G51">
-        <f t="shared" si="2"/>
         <v>3.38</v>
       </c>
-      <c r="H51">
-        <f t="shared" si="3"/>
-        <v>3.38</v>
-      </c>
       <c r="J51" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -5707,27 +5729,27 @@
         <v>1150</v>
       </c>
       <c r="F52">
+        <f t="shared" si="2"/>
+        <v>1.57</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="0"/>
+        <v>3.36</v>
+      </c>
+      <c r="H52">
         <f t="shared" si="1"/>
-        <v>1.57</v>
-      </c>
-      <c r="G52">
-        <f t="shared" si="2"/>
-        <v>3.36</v>
-      </c>
-      <c r="H52">
-        <f t="shared" si="3"/>
         <v>3.36</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -5736,27 +5758,27 @@
         <v>3938</v>
       </c>
       <c r="F53">
+        <f t="shared" si="2"/>
+        <v>2.04</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="0"/>
+        <v>4.37</v>
+      </c>
+      <c r="H53">
         <f t="shared" si="1"/>
-        <v>2.04</v>
-      </c>
-      <c r="G53">
-        <f t="shared" si="2"/>
-        <v>4.37</v>
-      </c>
-      <c r="H53">
-        <f t="shared" si="3"/>
         <v>4.37</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C54" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -5765,27 +5787,27 @@
         <v>6068</v>
       </c>
       <c r="F54">
+        <f t="shared" si="2"/>
+        <v>1.55</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="0"/>
+        <v>3.32</v>
+      </c>
+      <c r="H54">
         <f t="shared" si="1"/>
-        <v>1.55</v>
-      </c>
-      <c r="G54">
-        <f t="shared" si="2"/>
-        <v>3.32</v>
-      </c>
-      <c r="H54">
-        <f t="shared" si="3"/>
         <v>3.32</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C55" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -5794,27 +5816,27 @@
         <v>3142</v>
       </c>
       <c r="F55">
+        <f t="shared" si="2"/>
+        <v>1.28</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="0"/>
+        <v>2.75</v>
+      </c>
+      <c r="H55">
         <f t="shared" si="1"/>
-        <v>1.28</v>
-      </c>
-      <c r="G55">
-        <f t="shared" si="2"/>
-        <v>2.75</v>
-      </c>
-      <c r="H55">
-        <f t="shared" si="3"/>
         <v>2.75</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C56" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -5823,27 +5845,27 @@
         <v>1950</v>
       </c>
       <c r="F56">
+        <f t="shared" si="2"/>
+        <v>1.48</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="0"/>
+        <v>3.16</v>
+      </c>
+      <c r="H56">
         <f t="shared" si="1"/>
-        <v>1.48</v>
-      </c>
-      <c r="G56">
-        <f t="shared" si="2"/>
-        <v>3.16</v>
-      </c>
-      <c r="H56">
-        <f t="shared" si="3"/>
         <v>3.16</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C57" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -5852,27 +5874,27 @@
         <v>900</v>
       </c>
       <c r="F57">
+        <f t="shared" si="2"/>
+        <v>1.07</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="0"/>
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="H57">
         <f t="shared" si="1"/>
-        <v>1.07</v>
-      </c>
-      <c r="G57">
-        <f t="shared" si="2"/>
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="H57">
-        <f t="shared" si="3"/>
         <v>2.2999999999999998</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B58" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C58" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -5881,27 +5903,27 @@
         <v>1486</v>
       </c>
       <c r="F58">
+        <f t="shared" si="2"/>
+        <v>0.97</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="0"/>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H58">
         <f t="shared" si="1"/>
-        <v>0.97</v>
-      </c>
-      <c r="G58">
-        <f t="shared" si="2"/>
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="H58">
-        <f t="shared" si="3"/>
         <v>2.0699999999999998</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B59" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="C59" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -5910,15 +5932,15 @@
         <v>2744</v>
       </c>
       <c r="F59">
+        <f t="shared" si="2"/>
+        <v>1.63</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="0"/>
+        <v>3.5</v>
+      </c>
+      <c r="H59">
         <f t="shared" si="1"/>
-        <v>1.63</v>
-      </c>
-      <c r="G59">
-        <f t="shared" si="2"/>
-        <v>3.5</v>
-      </c>
-      <c r="H59">
-        <f t="shared" si="3"/>
         <v>3.5</v>
       </c>
     </row>
@@ -5947,63 +5969,63 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="H1" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="I1" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J1" s="21" t="s">
         <v>27</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="21" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B2" s="26">
         <v>1</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E2" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="G2" s="22" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H2" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I2" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J2" s="24">
         <v>1</v>
@@ -6011,31 +6033,31 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B3" s="26">
         <v>1</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I3" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J3" s="24">
         <v>-1</v>
@@ -6043,31 +6065,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B4" s="26">
         <v>1</v>
       </c>
       <c r="C4" s="26" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I4" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J4" s="24">
         <v>917</v>
@@ -6075,31 +6097,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B5" s="26">
         <v>1</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E5" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I5" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J5" s="24">
         <v>300</v>
@@ -6107,31 +6129,31 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B6" s="26">
         <v>1</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="G6" s="22" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>62</v>
-      </c>
       <c r="H6" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I6" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J6" s="24">
         <v>1</v>
@@ -6139,31 +6161,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B7" s="26">
         <v>1</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J7" s="24">
         <v>-1</v>
@@ -6171,31 +6193,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B8" s="26">
         <v>1</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G8" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J8" s="24">
         <v>551</v>
@@ -6203,31 +6225,31 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B9" s="26">
         <v>1</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J9" s="24">
         <v>300</v>
@@ -6235,31 +6257,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B10" s="26">
         <v>1</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="G10" s="22" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J10" s="24">
         <v>1</v>
@@ -6267,31 +6289,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B11" s="26">
         <v>1</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J11" s="24">
         <v>-1</v>
@@ -6299,31 +6321,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B12" s="26">
         <v>1</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J12" s="24">
         <v>2304</v>
@@ -6331,31 +6353,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B13" s="26">
         <v>1</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J13" s="24">
         <v>300</v>
@@ -6363,7 +6385,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B14" s="26">
         <v>1</v>
@@ -6372,22 +6394,22 @@
         <v>0</v>
       </c>
       <c r="D14" s="22" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F14" s="22" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G14" s="22" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J14" s="24">
         <v>1</v>
@@ -6395,7 +6417,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B15" s="26">
         <v>1</v>
@@ -6404,22 +6426,22 @@
         <v>0</v>
       </c>
       <c r="D15" s="22" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F15" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G15" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J15" s="24">
         <v>-1</v>
@@ -6427,7 +6449,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B16" s="26">
         <v>1</v>
@@ -6436,22 +6458,22 @@
         <v>0</v>
       </c>
       <c r="D16" s="22" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G16" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J16" s="24">
         <v>1428</v>
@@ -6459,7 +6481,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B17" s="26">
         <v>1</v>
@@ -6468,22 +6490,22 @@
         <v>0</v>
       </c>
       <c r="D17" s="22" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G17" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I17" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J17" s="24">
         <v>300</v>
@@ -6491,31 +6513,31 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B18" s="26">
         <v>1</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D18" s="22" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G18" s="22" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I18" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J18" s="24">
         <v>1</v>
@@ -6523,31 +6545,31 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B19" s="26">
         <v>1</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D19" s="22" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F19" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G19" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J19" s="24">
         <v>-1</v>
@@ -6555,31 +6577,31 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B20" s="26">
         <v>1</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F20" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G20" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J20" s="24">
         <v>851</v>
@@ -6587,31 +6609,31 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B21" s="26">
         <v>1</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F21" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G21" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I21" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J21" s="24">
         <v>300</v>
@@ -6619,31 +6641,31 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B22" s="26">
         <v>1</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F22" s="22" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G22" s="22" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J22" s="24">
         <v>1</v>
@@ -6651,31 +6673,31 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B23" s="26">
         <v>1</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D23" s="22" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F23" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G23" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I23" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J23" s="24">
         <v>-1</v>
@@ -6683,31 +6705,31 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B24" s="26">
         <v>1</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D24" s="22" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G24" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I24" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J24" s="24">
         <v>314</v>
@@ -6715,31 +6737,31 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B25" s="26">
         <v>1</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D25" s="22" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F25" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G25" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J25" s="24">
         <v>300</v>
@@ -6747,31 +6769,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B26" s="26">
         <v>1</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D26" s="22" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F26" s="22" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G26" s="22" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I26" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J26" s="24">
         <v>1</v>
@@ -6779,31 +6801,31 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B27" s="26">
         <v>1</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D27" s="22" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F27" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G27" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I27" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J27" s="24">
         <v>-1</v>
@@ -6811,31 +6833,31 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B28" s="26">
         <v>1</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F28" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G28" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J28" s="24">
         <v>1593</v>
@@ -6843,31 +6865,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B29" s="26">
         <v>1</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D29" s="22" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F29" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G29" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J29" s="24">
         <v>300</v>
@@ -6875,31 +6897,31 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B30" s="26">
         <v>1</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D30" s="22" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F30" s="22" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G30" s="22" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J30" s="24">
         <v>1</v>
@@ -6907,31 +6929,31 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B31" s="26">
         <v>1</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D31" s="22" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F31" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G31" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I31" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J31" s="24">
         <v>-1</v>
@@ -6939,31 +6961,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B32" s="26">
         <v>1</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D32" s="22" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F32" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I32" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J32" s="24">
         <v>15</v>
@@ -6971,31 +6993,31 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B33" s="26">
         <v>1</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D33" s="22" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I33" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J33" s="24">
         <v>300</v>
@@ -7003,7 +7025,7 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B34" s="26">
         <v>1</v>
@@ -7012,22 +7034,22 @@
         <v>0</v>
       </c>
       <c r="D34" s="22" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F34" s="22" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I34" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J34" s="24">
         <v>1</v>
@@ -7035,7 +7057,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B35" s="26">
         <v>1</v>
@@ -7044,22 +7066,22 @@
         <v>0</v>
       </c>
       <c r="D35" s="22" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F35" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G35" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J35" s="24">
         <v>-1</v>
@@ -7067,7 +7089,7 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B36" s="26">
         <v>1</v>
@@ -7076,22 +7098,22 @@
         <v>0</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F36" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G36" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I36" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J36" s="24">
         <v>31</v>
@@ -7099,7 +7121,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B37" s="26">
         <v>1</v>
@@ -7108,22 +7130,22 @@
         <v>0</v>
       </c>
       <c r="D37" s="22" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F37" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G37" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I37" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J37" s="24">
         <v>300</v>
@@ -7131,31 +7153,31 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B38" s="26">
         <v>1</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D38" s="22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F38" s="22" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="G38" s="22" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I38" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J38" s="24">
         <v>1</v>
@@ -7163,31 +7185,31 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B39" s="26">
         <v>1</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F39" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G39" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I39" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J39" s="24">
         <v>-1</v>
@@ -7195,31 +7217,31 @@
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B40" s="26">
         <v>1</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G40" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I40" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J40" s="24">
         <v>241</v>
@@ -7227,31 +7249,31 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B41" s="26">
         <v>1</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G41" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I41" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J41" s="24">
         <v>300</v>
@@ -7259,31 +7281,31 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B42" s="26">
         <v>1</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G42" s="22" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I42" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J42" s="24">
         <v>1</v>
@@ -7291,31 +7313,31 @@
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B43" s="26">
         <v>1</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G43" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I43" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J43" s="24">
         <v>-1</v>
@@ -7323,31 +7345,31 @@
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B44" s="26">
         <v>1</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G44" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J44" s="24">
         <v>418</v>
@@ -7355,31 +7377,31 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B45" s="26">
         <v>1</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G45" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J45" s="24">
         <v>300</v>
@@ -7387,31 +7409,31 @@
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B46" s="26">
         <v>1</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G46" s="22" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I46" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J46" s="24">
         <v>1</v>
@@ -7419,31 +7441,31 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B47" s="26">
         <v>1</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G47" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J47" s="24">
         <v>-1</v>
@@ -7451,31 +7473,31 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B48" s="26">
         <v>1</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E48" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I48" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J48" s="24">
         <v>800</v>
@@ -7483,31 +7505,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B49" s="26">
         <v>1</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I49" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J49" s="24">
         <v>300</v>
@@ -7515,31 +7537,31 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B50" s="26">
         <v>1</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I50" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J50" s="24">
         <v>1</v>
@@ -7547,31 +7569,31 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B51" s="26">
         <v>1</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E51" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I51" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J51" s="24">
         <v>-1</v>
@@ -7579,31 +7601,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B52" s="26">
         <v>1</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F52" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I52" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J52" s="24">
         <v>1000</v>
@@ -7611,31 +7633,31 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B53" s="26">
         <v>1</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F53" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J53" s="24">
         <v>300</v>
@@ -7643,31 +7665,31 @@
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B54" s="26">
         <v>1</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D54" s="22" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G54" s="22" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I54" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J54" s="24">
         <v>1</v>
@@ -7675,31 +7697,31 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B55" s="26">
         <v>1</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D55" s="22" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F55" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G55" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I55" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J55" s="24">
         <v>-1</v>
@@ -7707,31 +7729,31 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B56" s="26">
         <v>1</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G56" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J56" s="24">
         <v>530</v>
@@ -7739,31 +7761,31 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B57" s="26">
         <v>1</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D57" s="22" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G57" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J57" s="24">
         <v>300</v>
@@ -7771,31 +7793,31 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B58" s="26">
         <v>1</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D58" s="22" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="G58" s="22" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I58" s="23" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J58" s="24">
         <v>1</v>
@@ -7803,31 +7825,31 @@
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B59" s="26">
         <v>1</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G59" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I59" s="23" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J59" s="24">
         <v>-1</v>
@@ -7835,31 +7857,31 @@
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B60" s="26">
         <v>1</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D60" s="22" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G60" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I60" s="23" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J60" s="24">
         <v>20</v>
@@ -7867,31 +7889,31 @@
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B61" s="26">
         <v>1</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D61" s="22" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G61" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J61" s="24">
         <v>300</v>
